--- a/AI Audit Log_LEHUYHOANG.xlsx
+++ b/AI Audit Log_LEHUYHOANG.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tuần 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tuần 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>STT</t>
   </si>
@@ -53,6 +54,38 @@
 Trợ Lý AI Hỗ Trợ bán Hàng
 Hệ Thống Quản Trị (Admin)</t>
   </si>
+  <si>
+    <t xml:space="preserve">Vẽ figma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dựa trên những chức năng nãy 
+Quản lý Đặt Lịch Sửa Chữa
+Sàn Mua Bán Đồ Gia Dụng Cũ
+Trợ Lý AI Chẩn Đoán Lỗi
+Trợ Lý AI Hỗ Trợ bán Hàng
+Hệ Thống Quản Trị (Admin)
+ hãy hỗ trợ tôi vẽ figma 
+</t>
+  </si>
+  <si>
+    <t>1. Bản đồ các màn hình (Sitemap / Screen Flow)
+A. Giao diện Người dùng (User App)
+Module Đặt Lịch Sửa Chữa
+Module Sàn Đồ Gia Dụng Cũ
+Module Trợ Lý AI
+B. Hệ Thống Quản Trị (Admin Dashboard - Giao diện Web)
+Các màn hình Admin cần vẽ
+2. Hướng dẫn thiết kế các Component chính trong Figma
+Màn hình Mobile (User)
+Card Sản phẩm 
+Khung Chat AI
+Màn hình Web (Admin)
+3. Các bước triển khai thực tế trên Figma
+Bước 1: Thiết lập Màu sắc &amp; Font chữ (Design System)
+Bước 2: Vẽ Wireframe Low-fidelity (Khung xương trắng đen)
+Bước 3: Thiết kế High-fidelity (Giao diện chi tiết)
+Bước 4: Tạo Prototype (Nối hiệu ứng chuyển động)</t>
+  </si>
 </sst>
 </file>
 
@@ -64,7 +97,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,13 +111,6 @@
       <color indexed="8"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -549,155 +575,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1050,16 +1085,16 @@
       </c>
     </row>
     <row r="2" ht="72" spans="1:4">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1067,4 +1102,49 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="48.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="41.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="244.8" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>